--- a/reports/2026-02-28.xlsx
+++ b/reports/2026-02-28.xlsx
@@ -16,7 +16,7 @@
     <sheet name="Pullback Setups" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Global Top 20'!$A$1:$N$17</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Global Top 20'!$A$1:$N$18</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Reversal Setups'!$A$1:$U$11</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Breakout Setups'!$A$1:$U$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Breakout Immediate 1-5D'!$A$1:$U$1</definedName>
@@ -554,7 +554,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-02-28 18:47 UTC</t>
+          <t>2026-02-28 19:39 UTC</t>
         </is>
       </c>
     </row>
@@ -601,7 +601,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="15">
@@ -621,7 +621,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
   </sheetData>
@@ -635,7 +635,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N17"/>
+  <dimension ref="A1:N18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -740,18 +740,27 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>$2.39</t>
+          <t>$2.43</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>$1.30B</t>
+          <t>$1.33B</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>$5.69M</t>
-        </is>
+          <t>$5.64M</t>
+        </is>
+      </c>
+      <c r="K2" t="n">
+        <v>103704809.8059418</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0.0782157249686404</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0.05436412195875779</v>
       </c>
       <c r="N2" t="inlineStr"/>
     </row>
@@ -785,18 +794,27 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>$1.59</t>
+          <t>$1.63</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>$2.66B</t>
+          <t>$2.69B</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>$13.67M</t>
-        </is>
+          <t>$13.62M</t>
+        </is>
+      </c>
+      <c r="K3" t="n">
+        <v>316260942.1037241</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0.1177699609456559</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0.04308108869014706</v>
       </c>
       <c r="N3" t="inlineStr"/>
     </row>
@@ -806,12 +824,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>NEARUSDT</t>
+          <t>FILUSDT</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>NEAR Protocol</t>
+          <t>Filecoin</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -820,28 +838,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>46.79</v>
+        <v>46.88</v>
       </c>
       <c r="F4" t="n">
-        <v>46.79</v>
+        <v>46.88</v>
       </c>
       <c r="G4" t="n">
         <v>2</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>$1.10</t>
+          <t>$0.99</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>$1.41B</t>
+          <t>$738.12M</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>$5.82M</t>
-        </is>
+          <t>$5.06M</t>
+        </is>
+      </c>
+      <c r="K4" t="n">
+        <v>110147330.5474912</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0.149227046229576</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0.04596472996698801</v>
       </c>
       <c r="N4" t="inlineStr"/>
     </row>
@@ -851,12 +878,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>UNIUSDT</t>
+          <t>NEARUSDT</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Uniswap</t>
+          <t>NEAR Protocol</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -865,28 +892,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>41.3</v>
+        <v>46.79</v>
       </c>
       <c r="F5" t="n">
-        <v>41.3</v>
+        <v>46.79</v>
       </c>
       <c r="G5" t="n">
         <v>2</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>$3.75</t>
+          <t>$1.13</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>$2.37B</t>
+          <t>$1.43B</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>$7.50M</t>
-        </is>
+          <t>$6.42M</t>
+        </is>
+      </c>
+      <c r="K5" t="n">
+        <v>195827992.6785749</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0.1368086114584143</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0.0328010254950786</v>
       </c>
       <c r="N5" t="inlineStr"/>
     </row>
@@ -896,12 +932,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>AVAXUSDT</t>
+          <t>UNIUSDT</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Avalanche</t>
+          <t>Uniswap</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -910,28 +946,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>40.77</v>
+        <v>41.3</v>
       </c>
       <c r="F6" t="n">
-        <v>40.77</v>
+        <v>41.3</v>
       </c>
       <c r="G6" t="n">
         <v>2</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>$8.87</t>
+          <t>$3.81</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>$3.82B</t>
+          <t>$2.40B</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>$15.71M</t>
-        </is>
+          <t>$7.82M</t>
+        </is>
+      </c>
+      <c r="K6" t="n">
+        <v>198307758.1007269</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0.08254626240523591</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0.03942039780929451</v>
       </c>
       <c r="N6" t="inlineStr"/>
     </row>
@@ -941,12 +986,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>SUIUSDT</t>
+          <t>AVAXUSDT</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Sui</t>
+          <t>Avalanche</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -955,28 +1000,37 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>36.38</v>
+        <v>40.77</v>
       </c>
       <c r="F7" t="n">
-        <v>36.38</v>
+        <v>40.77</v>
       </c>
       <c r="G7" t="n">
         <v>2</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>$0.88</t>
+          <t>$8.96</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>$3.36B</t>
+          <t>$3.86B</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>$33.45M</t>
-        </is>
+          <t>$16.15M</t>
+        </is>
+      </c>
+      <c r="K7" t="n">
+        <v>358337163.9684699</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0.0929247210919846</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0.04506511043443127</v>
       </c>
       <c r="N7" t="inlineStr"/>
     </row>
@@ -986,12 +1040,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>LTCUSDT</t>
+          <t>SUIUSDT</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Litecoin</t>
+          <t>Sui</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1000,28 +1054,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>34.72</v>
+        <v>36.38</v>
       </c>
       <c r="F8" t="n">
-        <v>34.72</v>
+        <v>36.38</v>
       </c>
       <c r="G8" t="n">
         <v>2</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>$53.69</t>
+          <t>$0.89</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>$4.12B</t>
+          <t>$3.41B</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>$10.23M</t>
-        </is>
+          <t>$35.15M</t>
+        </is>
+      </c>
+      <c r="K8" t="n">
+        <v>882139518.5732399</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0.2585834066973651</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0.03984973701037225</v>
       </c>
       <c r="N8" t="inlineStr"/>
     </row>
@@ -1031,12 +1094,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>LINKUSDT</t>
+          <t>LTCUSDT</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Chainlink</t>
+          <t>Litecoin</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1045,28 +1108,37 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>34.09</v>
+        <v>34.72</v>
       </c>
       <c r="F9" t="n">
-        <v>34.09</v>
+        <v>34.72</v>
       </c>
       <c r="G9" t="n">
         <v>2</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>$8.59</t>
+          <t>$54.35</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>$6.07B</t>
+          <t>$4.16B</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>$19.84M</t>
-        </is>
+          <t>$10.27M</t>
+        </is>
+      </c>
+      <c r="K9" t="n">
+        <v>342312576.6380076</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0.08233653653539608</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0.03000262926611873</v>
       </c>
       <c r="N9" t="inlineStr"/>
     </row>
@@ -1076,12 +1148,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>ADAUSDT</t>
+          <t>LINKUSDT</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Cardano</t>
+          <t>Chainlink</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1090,28 +1162,37 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>33.52</v>
+        <v>34.09</v>
       </c>
       <c r="F10" t="n">
-        <v>33.52</v>
+        <v>34.09</v>
       </c>
       <c r="G10" t="n">
         <v>2</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>$0.27</t>
+          <t>$8.72</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>$9.80B</t>
+          <t>$6.15B</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>$18.64M</t>
-        </is>
+          <t>$20.56M</t>
+        </is>
+      </c>
+      <c r="K10" t="n">
+        <v>425919179.5128729</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0.06927366358639214</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0.04827381757383052</v>
       </c>
       <c r="N10" t="inlineStr"/>
     </row>
@@ -1121,12 +1202,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>AAVEUSDT</t>
+          <t>ADAUSDT</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Aave</t>
+          <t>Cardano</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1135,28 +1216,37 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>26.87</v>
+        <v>33.52</v>
       </c>
       <c r="F11" t="n">
-        <v>26.87</v>
+        <v>33.52</v>
       </c>
       <c r="G11" t="n">
         <v>2</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>$109.85</t>
+          <t>$0.28</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>$1.68B</t>
+          <t>$9.99B</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>$6.59M</t>
-        </is>
+          <t>$19.61M</t>
+        </is>
+      </c>
+      <c r="K11" t="n">
+        <v>653292338.7457236</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0.06542217554926215</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0.03001523684212707</v>
       </c>
       <c r="N11" t="inlineStr"/>
     </row>
@@ -1166,12 +1256,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>HYPEUSDT</t>
+          <t>AAVEUSDT</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Hyperliquid</t>
+          <t>Aave</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1180,28 +1270,37 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>25.5</v>
+        <v>26.87</v>
       </c>
       <c r="F12" t="n">
-        <v>25.5</v>
+        <v>26.87</v>
       </c>
       <c r="G12" t="n">
         <v>2</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>$29.28</t>
+          <t>$111.47</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>$7.61B</t>
+          <t>$1.70B</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>$10.26M</t>
-        </is>
+          <t>$6.86M</t>
+        </is>
+      </c>
+      <c r="K12" t="n">
+        <v>272532036.9319566</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0.1604458674424538</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0.02517435174681114</v>
       </c>
       <c r="N12" t="inlineStr"/>
     </row>
@@ -1211,12 +1310,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>PEPEUSDT</t>
+          <t>HYPEUSDT</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Pepe</t>
+          <t>Hyperliquid</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1225,28 +1324,37 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>25.32</v>
+        <v>25.5</v>
       </c>
       <c r="F13" t="n">
-        <v>25.32</v>
+        <v>25.5</v>
       </c>
       <c r="G13" t="n">
         <v>2</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>$0.00</t>
+          <t>$29.63</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>$1.48B</t>
+          <t>$7.64B</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>$12.47M</t>
-        </is>
+          <t>$10.49M</t>
+        </is>
+      </c>
+      <c r="K13" t="n">
+        <v>281053308.7631427</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0.03678841593449271</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0.03731472988577504</v>
       </c>
       <c r="N13" t="inlineStr"/>
     </row>
@@ -1256,12 +1364,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>ZECUSDT</t>
+          <t>PEPEUSDT</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Zcash</t>
+          <t>Pepe</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1270,28 +1378,37 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>23.78</v>
+        <v>25.32</v>
       </c>
       <c r="F14" t="n">
-        <v>23.78</v>
+        <v>25.32</v>
       </c>
       <c r="G14" t="n">
         <v>2</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>$212.56</t>
+          <t>$0.00</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>$3.52B</t>
+          <t>$1.50B</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>$7.97M</t>
-        </is>
+          <t>$12.71M</t>
+        </is>
+      </c>
+      <c r="K14" t="n">
+        <v>361655228.1612801</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0.2409313725156719</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0.03513818485075368</v>
       </c>
       <c r="N14" t="inlineStr"/>
     </row>
@@ -1301,12 +1418,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>BCHUSDT</t>
+          <t>ZECUSDT</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Bitcoin Cash</t>
+          <t>Zcash</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1315,28 +1432,37 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>22.89</v>
+        <v>23.78</v>
       </c>
       <c r="F15" t="n">
-        <v>22.89</v>
+        <v>23.78</v>
       </c>
       <c r="G15" t="n">
         <v>2</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>$448.70</t>
+          <t>$218.26</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>$8.96B</t>
+          <t>$3.60B</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>$7.98M</t>
-        </is>
+          <t>$8.02M</t>
+        </is>
+      </c>
+      <c r="K15" t="n">
+        <v>278129374.5148109</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0.07734238896335062</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0.02885315495351485</v>
       </c>
       <c r="N15" t="inlineStr"/>
     </row>
@@ -1346,48 +1472,53 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>APTUSDT</t>
+          <t>BCHUSDT</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Aptos</t>
+          <t>Bitcoin Cash</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>pullback</t>
+          <t>reversal</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>7.17</v>
+        <v>22.89</v>
       </c>
       <c r="F16" t="n">
-        <v>7.17</v>
+        <v>22.89</v>
       </c>
       <c r="G16" t="n">
         <v>2</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>$0.92</t>
+          <t>$449.80</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>$717.33M</t>
+          <t>$8.96B</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>$7.42M</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>broken_trend</t>
-        </is>
-      </c>
+          <t>$8.48M</t>
+        </is>
+      </c>
+      <c r="K16" t="n">
+        <v>347712911.8013508</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0.03882366612174434</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0.0244021415714567</v>
+      </c>
+      <c r="N16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -1395,12 +1526,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>CHZUSDT</t>
+          <t>APTUSDT</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Chiliz</t>
+          <t>Aptos</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1409,37 +1540,104 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>2.8</v>
+        <v>7.17</v>
       </c>
       <c r="F17" t="n">
-        <v>2.8</v>
+        <v>7.17</v>
       </c>
       <c r="G17" t="n">
         <v>2</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
+          <t>$0.95</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>$734.07M</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>$7.48M</t>
+        </is>
+      </c>
+      <c r="K17" t="n">
+        <v>115983341.9898674</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0.1579997935955454</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0.06445004379898836</v>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>broken_trend</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>CHZUSDT</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Chiliz</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>pullback</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="F18" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="G18" t="n">
+        <v>2</v>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
           <t>$0.03</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>$347.94M</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>$5.44M</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr">
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>$352.06M</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>$5.36M</t>
+        </is>
+      </c>
+      <c r="K18" t="n">
+        <v>81991447.07341987</v>
+      </c>
+      <c r="L18" t="n">
+        <v>0.2328886242633493</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0.06536321737218567</v>
+      </c>
+      <c r="N18" t="inlineStr">
         <is>
           <t>broken_trend</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:N17"/>
+  <autoFilter ref="A1:N18"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1599,7 +1797,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>$2.39</t>
+          <t>$2.43</t>
         </is>
       </c>
       <c r="E2" t="b">
@@ -1607,13 +1805,22 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>$1.30B</t>
+          <t>$1.33B</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>$5.69M</t>
-        </is>
+          <t>$5.64M</t>
+        </is>
+      </c>
+      <c r="M2" t="n">
+        <v>103704809.8059418</v>
+      </c>
+      <c r="N2" t="n">
+        <v>0.0782157249686404</v>
+      </c>
+      <c r="O2" t="n">
+        <v>0.05436412195875779</v>
       </c>
       <c r="P2" t="n">
         <v>72.15000000000001</v>
@@ -1648,7 +1855,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>$1.59</t>
+          <t>$1.63</t>
         </is>
       </c>
       <c r="E3" t="b">
@@ -1656,13 +1863,22 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>$2.66B</t>
+          <t>$2.69B</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>$13.67M</t>
-        </is>
+          <t>$13.62M</t>
+        </is>
+      </c>
+      <c r="M3" t="n">
+        <v>316260942.1037241</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0.1177699609456559</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0.04308108869014706</v>
       </c>
       <c r="P3" t="n">
         <v>67.8</v>
@@ -1687,17 +1903,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>NEARUSDT</t>
+          <t>FILUSDT</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>NEAR Protocol</t>
+          <t>Filecoin</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>$1.10</t>
+          <t>$0.99</t>
         </is>
       </c>
       <c r="E4" t="b">
@@ -1705,25 +1921,34 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>$1.41B</t>
+          <t>$738.12M</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>$5.82M</t>
-        </is>
+          <t>$5.06M</t>
+        </is>
+      </c>
+      <c r="M4" t="n">
+        <v>110147330.5474912</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0.149227046229576</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0.04596472996698801</v>
       </c>
       <c r="P4" t="n">
-        <v>46.79</v>
+        <v>46.88</v>
       </c>
       <c r="Q4" t="n">
         <v>100</v>
       </c>
       <c r="R4" t="n">
-        <v>78.84999999999999</v>
+        <v>79.16</v>
       </c>
       <c r="S4" t="n">
-        <v>57.84</v>
+        <v>57.82</v>
       </c>
       <c r="T4" t="n">
         <v>0</v>
@@ -1736,17 +1961,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>UNIUSDT</t>
+          <t>NEARUSDT</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Uniswap</t>
+          <t>NEAR Protocol</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>$3.75</t>
+          <t>$1.13</t>
         </is>
       </c>
       <c r="E5" t="b">
@@ -1754,25 +1979,34 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>$2.37B</t>
+          <t>$1.43B</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>$7.50M</t>
-        </is>
+          <t>$6.42M</t>
+        </is>
+      </c>
+      <c r="M5" t="n">
+        <v>195827992.6785749</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0.1368086114584143</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0.0328010254950786</v>
       </c>
       <c r="P5" t="n">
-        <v>41.3</v>
+        <v>46.79</v>
       </c>
       <c r="Q5" t="n">
         <v>100</v>
       </c>
       <c r="R5" t="n">
-        <v>78.42</v>
+        <v>78.84999999999999</v>
       </c>
       <c r="S5" t="n">
-        <v>44.44</v>
+        <v>57.84</v>
       </c>
       <c r="T5" t="n">
         <v>0</v>
@@ -1785,17 +2019,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>AVAXUSDT</t>
+          <t>UNIUSDT</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Avalanche</t>
+          <t>Uniswap</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>$8.87</t>
+          <t>$3.81</t>
         </is>
       </c>
       <c r="E6" t="b">
@@ -1803,28 +2037,37 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>$3.82B</t>
+          <t>$2.40B</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>$15.71M</t>
-        </is>
+          <t>$7.82M</t>
+        </is>
+      </c>
+      <c r="M6" t="n">
+        <v>198307758.1007269</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0.08254626240523591</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0.03942039780929451</v>
       </c>
       <c r="P6" t="n">
-        <v>40.77</v>
+        <v>41.3</v>
       </c>
       <c r="Q6" t="n">
         <v>100</v>
       </c>
       <c r="R6" t="n">
-        <v>85.14</v>
+        <v>78.42</v>
       </c>
       <c r="S6" t="n">
-        <v>20</v>
+        <v>44.44</v>
       </c>
       <c r="T6" t="n">
-        <v>24.1</v>
+        <v>0</v>
       </c>
       <c r="U6" t="inlineStr"/>
     </row>
@@ -1834,17 +2077,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>SUIUSDT</t>
+          <t>AVAXUSDT</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Sui</t>
+          <t>Avalanche</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>$0.88</t>
+          <t>$8.96</t>
         </is>
       </c>
       <c r="E7" t="b">
@@ -1852,28 +2095,37 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>$3.36B</t>
+          <t>$3.86B</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>$33.45M</t>
-        </is>
+          <t>$16.15M</t>
+        </is>
+      </c>
+      <c r="M7" t="n">
+        <v>358337163.9684699</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0.0929247210919846</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0.04506511043443127</v>
       </c>
       <c r="P7" t="n">
-        <v>36.38</v>
+        <v>40.77</v>
       </c>
       <c r="Q7" t="n">
         <v>100</v>
       </c>
       <c r="R7" t="n">
-        <v>87.31</v>
+        <v>85.14</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="T7" t="n">
-        <v>33.96</v>
+        <v>24.1</v>
       </c>
       <c r="U7" t="inlineStr"/>
     </row>
@@ -1883,17 +2135,17 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>LTCUSDT</t>
+          <t>SUIUSDT</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Litecoin</t>
+          <t>Sui</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>$53.69</t>
+          <t>$0.89</t>
         </is>
       </c>
       <c r="E8" t="b">
@@ -1901,28 +2153,37 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>$4.12B</t>
+          <t>$3.41B</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>$10.23M</t>
-        </is>
+          <t>$35.15M</t>
+        </is>
+      </c>
+      <c r="M8" t="n">
+        <v>882139518.5732399</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0.2585834066973651</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0.03984973701037225</v>
       </c>
       <c r="P8" t="n">
-        <v>34.72</v>
+        <v>36.38</v>
       </c>
       <c r="Q8" t="n">
         <v>100</v>
       </c>
       <c r="R8" t="n">
-        <v>89.06999999999999</v>
+        <v>87.31</v>
       </c>
       <c r="S8" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>33.96</v>
       </c>
       <c r="U8" t="inlineStr"/>
     </row>
@@ -1932,17 +2193,17 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>LINKUSDT</t>
+          <t>LTCUSDT</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Chainlink</t>
+          <t>Litecoin</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>$8.59</t>
+          <t>$54.35</t>
         </is>
       </c>
       <c r="E9" t="b">
@@ -1950,22 +2211,31 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>$6.07B</t>
+          <t>$4.16B</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>$19.84M</t>
-        </is>
+          <t>$10.27M</t>
+        </is>
+      </c>
+      <c r="M9" t="n">
+        <v>342312576.6380076</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0.08233653653539608</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0.03000262926611873</v>
       </c>
       <c r="P9" t="n">
-        <v>34.09</v>
+        <v>34.72</v>
       </c>
       <c r="Q9" t="n">
         <v>100</v>
       </c>
       <c r="R9" t="n">
-        <v>86.95999999999999</v>
+        <v>89.06999999999999</v>
       </c>
       <c r="S9" t="n">
         <v>20</v>
@@ -1981,17 +2251,17 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>ADAUSDT</t>
+          <t>LINKUSDT</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Cardano</t>
+          <t>Chainlink</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>$0.27</t>
+          <t>$8.72</t>
         </is>
       </c>
       <c r="E10" t="b">
@@ -1999,22 +2269,31 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>$9.80B</t>
+          <t>$6.15B</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>$18.64M</t>
-        </is>
+          <t>$20.56M</t>
+        </is>
+      </c>
+      <c r="M10" t="n">
+        <v>425919179.5128729</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0.06927366358639214</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0.04827381757383052</v>
       </c>
       <c r="P10" t="n">
-        <v>33.52</v>
+        <v>34.09</v>
       </c>
       <c r="Q10" t="n">
         <v>100</v>
       </c>
       <c r="R10" t="n">
-        <v>85.06999999999999</v>
+        <v>86.95999999999999</v>
       </c>
       <c r="S10" t="n">
         <v>20</v>
@@ -2030,17 +2309,17 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>AAVEUSDT</t>
+          <t>ADAUSDT</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Aave</t>
+          <t>Cardano</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>$109.85</t>
+          <t>$0.28</t>
         </is>
       </c>
       <c r="E11" t="b">
@@ -2048,25 +2327,34 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>$1.68B</t>
+          <t>$9.99B</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>$6.59M</t>
-        </is>
+          <t>$19.61M</t>
+        </is>
+      </c>
+      <c r="M11" t="n">
+        <v>653292338.7457236</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0.06542217554926215</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0.03001523684212707</v>
       </c>
       <c r="P11" t="n">
-        <v>26.87</v>
+        <v>33.52</v>
       </c>
       <c r="Q11" t="n">
         <v>100</v>
       </c>
       <c r="R11" t="n">
-        <v>89.56999999999999</v>
+        <v>85.06999999999999</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="T11" t="n">
         <v>0</v>
@@ -2669,7 +2957,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>$1.10</t>
+          <t>$1.13</t>
         </is>
       </c>
       <c r="E2" t="b">
@@ -2677,13 +2965,22 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>$1.41B</t>
+          <t>$1.43B</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>$5.82M</t>
-        </is>
+          <t>$6.42M</t>
+        </is>
+      </c>
+      <c r="M2" t="n">
+        <v>195827992.6785749</v>
+      </c>
+      <c r="N2" t="n">
+        <v>0.1368086114584143</v>
+      </c>
+      <c r="O2" t="n">
+        <v>0.0328010254950786</v>
       </c>
       <c r="P2" t="n">
         <v>24.78</v>
@@ -2712,17 +3009,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>ADAUSDT</t>
+          <t>FILUSDT</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Cardano</t>
+          <t>Filecoin</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>$0.27</t>
+          <t>$0.99</t>
         </is>
       </c>
       <c r="E3" t="b">
@@ -2730,16 +3027,25 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>$9.80B</t>
+          <t>$738.12M</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>$18.64M</t>
-        </is>
+          <t>$5.06M</t>
+        </is>
+      </c>
+      <c r="M3" t="n">
+        <v>110147330.5474912</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0.149227046229576</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0.04596472996698801</v>
       </c>
       <c r="P3" t="n">
-        <v>22.4</v>
+        <v>24.78</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
@@ -2748,10 +3054,10 @@
         <v>100</v>
       </c>
       <c r="S3" t="n">
-        <v>24</v>
+        <v>47.82</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>7.39</v>
       </c>
       <c r="U3" t="inlineStr">
         <is>
@@ -2765,17 +3071,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>LTCUSDT</t>
+          <t>ADAUSDT</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Litecoin</t>
+          <t>Cardano</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>$53.69</t>
+          <t>$0.28</t>
         </is>
       </c>
       <c r="E4" t="b">
@@ -2783,13 +3089,22 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>$4.12B</t>
+          <t>$9.99B</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>$10.23M</t>
-        </is>
+          <t>$19.61M</t>
+        </is>
+      </c>
+      <c r="M4" t="n">
+        <v>653292338.7457236</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0.06542217554926215</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0.03001523684212707</v>
       </c>
       <c r="P4" t="n">
         <v>22.4</v>
@@ -2818,17 +3133,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>DOTUSDT</t>
+          <t>LTCUSDT</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Polkadot</t>
+          <t>Litecoin</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>$1.59</t>
+          <t>$54.35</t>
         </is>
       </c>
       <c r="E5" t="b">
@@ -2836,28 +3151,37 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>$2.66B</t>
+          <t>$4.16B</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>$13.67M</t>
-        </is>
+          <t>$10.27M</t>
+        </is>
+      </c>
+      <c r="M5" t="n">
+        <v>342312576.6380076</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0.08233653653539608</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0.03000262926611873</v>
       </c>
       <c r="P5" t="n">
-        <v>22</v>
+        <v>22.4</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="S5" t="n">
-        <v>60</v>
+        <v>24</v>
       </c>
       <c r="T5" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="U5" t="inlineStr">
         <is>
@@ -2871,17 +3195,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>ICPUSDT</t>
+          <t>DOTUSDT</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Internet Computer</t>
+          <t>Polkadot</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>$2.39</t>
+          <t>$1.63</t>
         </is>
       </c>
       <c r="E6" t="b">
@@ -2889,28 +3213,37 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>$1.30B</t>
+          <t>$2.69B</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>$5.69M</t>
-        </is>
+          <t>$13.62M</t>
+        </is>
+      </c>
+      <c r="M6" t="n">
+        <v>316260942.1037241</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0.1177699609456559</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0.04308108869014706</v>
       </c>
       <c r="P6" t="n">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>10</v>
+        <v>80</v>
       </c>
       <c r="S6" t="n">
         <v>60</v>
       </c>
       <c r="T6" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="U6" t="inlineStr">
         <is>
@@ -2924,17 +3257,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>UNIUSDT</t>
+          <t>ICPUSDT</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Uniswap</t>
+          <t>Internet Computer</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>$3.75</t>
+          <t>$2.43</t>
         </is>
       </c>
       <c r="E7" t="b">
@@ -2942,16 +3275,25 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>$2.37B</t>
+          <t>$1.33B</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>$7.50M</t>
-        </is>
+          <t>$5.64M</t>
+        </is>
+      </c>
+      <c r="M7" t="n">
+        <v>103704809.8059418</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0.0782157249686404</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0.05436412195875779</v>
       </c>
       <c r="P7" t="n">
-        <v>7.44</v>
+        <v>8</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
@@ -2960,10 +3302,10 @@
         <v>10</v>
       </c>
       <c r="S7" t="n">
-        <v>54.44</v>
+        <v>60</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="U7" t="inlineStr">
         <is>
@@ -2977,17 +3319,17 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>APTUSDT</t>
+          <t>UNIUSDT</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Aptos</t>
+          <t>Uniswap</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>$0.92</t>
+          <t>$3.81</t>
         </is>
       </c>
       <c r="E8" t="b">
@@ -2995,16 +3337,25 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>$717.33M</t>
+          <t>$2.40B</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>$7.42M</t>
-        </is>
+          <t>$7.82M</t>
+        </is>
+      </c>
+      <c r="M8" t="n">
+        <v>198307758.1007269</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0.08254626240523591</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0.03942039780929451</v>
       </c>
       <c r="P8" t="n">
-        <v>7.17</v>
+        <v>7.44</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -3013,10 +3364,10 @@
         <v>10</v>
       </c>
       <c r="S8" t="n">
-        <v>51.67</v>
+        <v>54.44</v>
       </c>
       <c r="T8" t="n">
-        <v>31.38</v>
+        <v>0</v>
       </c>
       <c r="U8" t="inlineStr">
         <is>
@@ -3030,17 +3381,17 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>HYPEUSDT</t>
+          <t>APTUSDT</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Hyperliquid</t>
+          <t>Aptos</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>$29.28</t>
+          <t>$0.95</t>
         </is>
       </c>
       <c r="E9" t="b">
@@ -3048,16 +3399,25 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>$7.61B</t>
+          <t>$734.07M</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>$10.26M</t>
-        </is>
+          <t>$7.48M</t>
+        </is>
+      </c>
+      <c r="M9" t="n">
+        <v>115983341.9898674</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0.1579997935955454</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0.06445004379898836</v>
       </c>
       <c r="P9" t="n">
-        <v>5.2</v>
+        <v>7.17</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
@@ -3066,10 +3426,10 @@
         <v>10</v>
       </c>
       <c r="S9" t="n">
-        <v>32</v>
+        <v>51.67</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>31.38</v>
       </c>
       <c r="U9" t="inlineStr">
         <is>
@@ -3083,17 +3443,17 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>SUIUSDT</t>
+          <t>HYPEUSDT</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Sui</t>
+          <t>Hyperliquid</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>$0.88</t>
+          <t>$29.63</t>
         </is>
       </c>
       <c r="E10" t="b">
@@ -3101,16 +3461,25 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>$3.36B</t>
+          <t>$7.64B</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>$33.45M</t>
-        </is>
+          <t>$10.49M</t>
+        </is>
+      </c>
+      <c r="M10" t="n">
+        <v>281053308.7631427</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0.03678841593449271</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0.03731472988577504</v>
       </c>
       <c r="P10" t="n">
-        <v>4.4</v>
+        <v>5.2</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
@@ -3119,10 +3488,10 @@
         <v>10</v>
       </c>
       <c r="S10" t="n">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="T10" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="U10" t="inlineStr">
         <is>
@@ -3136,17 +3505,17 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>LINKUSDT</t>
+          <t>SUIUSDT</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Chainlink</t>
+          <t>Sui</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>$8.59</t>
+          <t>$0.89</t>
         </is>
       </c>
       <c r="E11" t="b">
@@ -3154,13 +3523,22 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>$6.07B</t>
+          <t>$3.41B</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>$19.84M</t>
-        </is>
+          <t>$35.15M</t>
+        </is>
+      </c>
+      <c r="M11" t="n">
+        <v>882139518.5732399</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0.2585834066973651</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0.03984973701037225</v>
       </c>
       <c r="P11" t="n">
         <v>4.4</v>
@@ -3175,7 +3553,7 @@
         <v>24</v>
       </c>
       <c r="T11" t="n">
-        <v>19.7</v>
+        <v>80</v>
       </c>
       <c r="U11" t="inlineStr">
         <is>
